--- a/code/cmb/lowl_litebird_fisher.xlsx
+++ b/code/cmb/lowl_litebird_fisher.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42258.72362793139</v>
+        <v>26635.83504272386</v>
       </c>
       <c r="C2" t="n">
-        <v>-103789.9680139472</v>
+        <v>-63225.5911794472</v>
       </c>
       <c r="D2" t="n">
-        <v>26227.65973072703</v>
+        <v>16796.28229150696</v>
       </c>
       <c r="E2" t="n">
-        <v>27524.6041418499</v>
+        <v>18324.26239095511</v>
       </c>
       <c r="F2" t="n">
-        <v>-21055.55104438361</v>
+        <v>-13354.66534565932</v>
       </c>
       <c r="G2" t="n">
-        <v>-5757.950808354386</v>
+        <v>-3615.741682539634</v>
       </c>
       <c r="H2" t="n">
-        <v>-1172.733113911139</v>
+        <v>-742.450883012911</v>
       </c>
       <c r="I2" t="n">
-        <v>5399.79154301773</v>
+        <v>-375.3641733404388</v>
       </c>
       <c r="J2" t="n">
-        <v>-5709.694399872941</v>
+        <v>-3671.314302178856</v>
       </c>
       <c r="K2" t="n">
-        <v>-1702.551814769709</v>
+        <v>-1095.234423138301</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-103789.9680139472</v>
+        <v>-63225.5911794472</v>
       </c>
       <c r="C3" t="n">
-        <v>298199.7893684559</v>
+        <v>192258.5835176627</v>
       </c>
       <c r="D3" t="n">
-        <v>-56842.80859286986</v>
+        <v>-32232.7296429599</v>
       </c>
       <c r="E3" t="n">
-        <v>-60736.27597363371</v>
+        <v>-37302.75566277435</v>
       </c>
       <c r="F3" t="n">
-        <v>48109.42018780332</v>
+        <v>28365.26115083661</v>
       </c>
       <c r="G3" t="n">
-        <v>13224.51738177658</v>
+        <v>7742.363386742604</v>
       </c>
       <c r="H3" t="n">
-        <v>2727.308238968988</v>
+        <v>1595.203660075774</v>
       </c>
       <c r="I3" t="n">
-        <v>-109836.3818607053</v>
+        <v>-95080.75331024281</v>
       </c>
       <c r="J3" t="n">
-        <v>13231.94173503875</v>
+        <v>8069.477839166821</v>
       </c>
       <c r="K3" t="n">
-        <v>3913.439662905243</v>
+        <v>2373.26975859496</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26227.65973072703</v>
+        <v>16796.28229150696</v>
       </c>
       <c r="C4" t="n">
-        <v>-56842.80859286986</v>
+        <v>-32232.7296429599</v>
       </c>
       <c r="D4" t="n">
-        <v>18018.38069701673</v>
+        <v>12263.10129766854</v>
       </c>
       <c r="E4" t="n">
-        <v>18067.15641677838</v>
+        <v>12559.23975889816</v>
       </c>
       <c r="F4" t="n">
-        <v>-13578.37869407795</v>
+        <v>-8954.053575117359</v>
       </c>
       <c r="G4" t="n">
-        <v>-3678.136129390323</v>
+        <v>-2396.911310779147</v>
       </c>
       <c r="H4" t="n">
-        <v>-778.9913493026609</v>
+        <v>-515.3245926721256</v>
       </c>
       <c r="I4" t="n">
-        <v>-15695.81884607141</v>
+        <v>-19153.30783241551</v>
       </c>
       <c r="J4" t="n">
-        <v>-3533.676136643541</v>
+        <v>-2332.805319233035</v>
       </c>
       <c r="K4" t="n">
-        <v>-1064.114214607805</v>
+        <v>-705.5768875734933</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27524.6041418499</v>
+        <v>18324.26239095511</v>
       </c>
       <c r="C5" t="n">
-        <v>-60736.27597363371</v>
+        <v>-37302.75566277435</v>
       </c>
       <c r="D5" t="n">
-        <v>18067.15641677838</v>
+        <v>12559.23975889817</v>
       </c>
       <c r="E5" t="n">
-        <v>19994.12842183639</v>
+        <v>14189.27425437648</v>
       </c>
       <c r="F5" t="n">
-        <v>-14673.89527186936</v>
+        <v>-9924.153298556175</v>
       </c>
       <c r="G5" t="n">
-        <v>-4016.379463430802</v>
+        <v>-2691.188532416708</v>
       </c>
       <c r="H5" t="n">
-        <v>-766.0251069147898</v>
+        <v>-522.5046977742948</v>
       </c>
       <c r="I5" t="n">
-        <v>-9994.008208937614</v>
+        <v>-13593.97433666013</v>
       </c>
       <c r="J5" t="n">
-        <v>-4007.827534593903</v>
+        <v>-2715.894454246598</v>
       </c>
       <c r="K5" t="n">
-        <v>-1196.777981199545</v>
+        <v>-812.9818093423643</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-21055.55104438361</v>
+        <v>-13354.66534565932</v>
       </c>
       <c r="C6" t="n">
-        <v>48109.42018780333</v>
+        <v>28365.26115083661</v>
       </c>
       <c r="D6" t="n">
-        <v>-13578.37869407795</v>
+        <v>-8954.053575117361</v>
       </c>
       <c r="E6" t="n">
-        <v>-14673.89527186936</v>
+        <v>-9924.153298556173</v>
       </c>
       <c r="F6" t="n">
-        <v>11014.72674486949</v>
+        <v>7099.160932731075</v>
       </c>
       <c r="G6" t="n">
-        <v>3018.689800174659</v>
+        <v>1927.373597247639</v>
       </c>
       <c r="H6" t="n">
-        <v>584.6117198488249</v>
+        <v>377.9564944850189</v>
       </c>
       <c r="I6" t="n">
-        <v>4167.971013940424</v>
+        <v>7125.546979552621</v>
       </c>
       <c r="J6" t="n">
-        <v>2999.662201867496</v>
+        <v>1944.339975473618</v>
       </c>
       <c r="K6" t="n">
-        <v>895.4795625961023</v>
+        <v>581.6680023611037</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5757.950808354386</v>
+        <v>-3615.741682539634</v>
       </c>
       <c r="C7" t="n">
-        <v>13224.51738177658</v>
+        <v>7742.363386742604</v>
       </c>
       <c r="D7" t="n">
-        <v>-3678.136129390323</v>
+        <v>-2396.911310779147</v>
       </c>
       <c r="E7" t="n">
-        <v>-4016.379463430802</v>
+        <v>-2691.188532416708</v>
       </c>
       <c r="F7" t="n">
-        <v>3018.689800174659</v>
+        <v>1927.37359724764</v>
       </c>
       <c r="G7" t="n">
-        <v>829.5370411241787</v>
+        <v>524.9412056154989</v>
       </c>
       <c r="H7" t="n">
-        <v>158.1419012209064</v>
+        <v>100.9831354590723</v>
       </c>
       <c r="I7" t="n">
-        <v>866.5133014131926</v>
+        <v>1691.681716690567</v>
       </c>
       <c r="J7" t="n">
-        <v>828.2795313246196</v>
+        <v>532.2204246058657</v>
       </c>
       <c r="K7" t="n">
-        <v>246.9352455707883</v>
+        <v>158.9602414618649</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1172.733113911139</v>
+        <v>-742.4508830129109</v>
       </c>
       <c r="C8" t="n">
-        <v>2727.308238968988</v>
+        <v>1595.203660075774</v>
       </c>
       <c r="D8" t="n">
-        <v>-778.9913493026608</v>
+        <v>-515.3245926721255</v>
       </c>
       <c r="E8" t="n">
-        <v>-766.0251069147897</v>
+        <v>-522.5046977742948</v>
       </c>
       <c r="F8" t="n">
-        <v>584.6117198488249</v>
+        <v>377.9564944850188</v>
       </c>
       <c r="G8" t="n">
-        <v>158.1419012209064</v>
+        <v>100.9831354590723</v>
       </c>
       <c r="H8" t="n">
-        <v>34.67285230097833</v>
+        <v>22.43692338340902</v>
       </c>
       <c r="I8" t="n">
-        <v>334.5466000203244</v>
+        <v>488.2591673792758</v>
       </c>
       <c r="J8" t="n">
-        <v>151.2196848225757</v>
+        <v>98.32960748702564</v>
       </c>
       <c r="K8" t="n">
-        <v>45.49515583855788</v>
+        <v>29.67849902077197</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5399.791543017729</v>
+        <v>-375.3641733404369</v>
       </c>
       <c r="C9" t="n">
-        <v>-109836.3818607053</v>
+        <v>-95080.75331024281</v>
       </c>
       <c r="D9" t="n">
-        <v>-15695.81884607141</v>
+        <v>-19153.30783241551</v>
       </c>
       <c r="E9" t="n">
-        <v>-9994.008208937614</v>
+        <v>-13593.97433666013</v>
       </c>
       <c r="F9" t="n">
-        <v>4167.971013940425</v>
+        <v>7125.546979552621</v>
       </c>
       <c r="G9" t="n">
-        <v>866.5133014131933</v>
+        <v>1691.681716690567</v>
       </c>
       <c r="H9" t="n">
-        <v>334.5466000203245</v>
+        <v>488.2591673792757</v>
       </c>
       <c r="I9" t="n">
-        <v>249046.5310593633</v>
+        <v>246807.1309815477</v>
       </c>
       <c r="J9" t="n">
-        <v>98.37814751369504</v>
+        <v>900.776518185023</v>
       </c>
       <c r="K9" t="n">
-        <v>124.6123412867557</v>
+        <v>363.0495181898507</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-5709.694399872941</v>
+        <v>-3671.314302178855</v>
       </c>
       <c r="C10" t="n">
-        <v>13231.94173503875</v>
+        <v>8069.477839166821</v>
       </c>
       <c r="D10" t="n">
-        <v>-3533.676136643541</v>
+        <v>-2332.805319233035</v>
       </c>
       <c r="E10" t="n">
-        <v>-4007.827534593903</v>
+        <v>-2715.894454246598</v>
       </c>
       <c r="F10" t="n">
-        <v>2999.662201867496</v>
+        <v>1944.339975473618</v>
       </c>
       <c r="G10" t="n">
-        <v>828.2795313246196</v>
+        <v>532.2204246058658</v>
       </c>
       <c r="H10" t="n">
-        <v>151.2196848225757</v>
+        <v>98.32960748702564</v>
       </c>
       <c r="I10" t="n">
-        <v>98.37814751369454</v>
+        <v>900.776518185023</v>
       </c>
       <c r="J10" t="n">
-        <v>850.9916107302095</v>
+        <v>557.0952018294593</v>
       </c>
       <c r="K10" t="n">
-        <v>252.6208939122576</v>
+        <v>165.5280103222105</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1702.551814769708</v>
+        <v>-1095.234423138301</v>
       </c>
       <c r="C11" t="n">
-        <v>3913.439662905243</v>
+        <v>2373.26975859496</v>
       </c>
       <c r="D11" t="n">
-        <v>-1064.114214607805</v>
+        <v>-705.5768875734935</v>
       </c>
       <c r="E11" t="n">
-        <v>-1196.777981199545</v>
+        <v>-812.9818093423642</v>
       </c>
       <c r="F11" t="n">
-        <v>895.4795625961023</v>
+        <v>581.6680023611037</v>
       </c>
       <c r="G11" t="n">
-        <v>246.9352455707882</v>
+        <v>158.9602414618649</v>
       </c>
       <c r="H11" t="n">
-        <v>45.49515583855788</v>
+        <v>29.67849902077197</v>
       </c>
       <c r="I11" t="n">
-        <v>124.6123412867556</v>
+        <v>363.0495181898508</v>
       </c>
       <c r="J11" t="n">
-        <v>252.6208939122576</v>
+        <v>165.5280103222105</v>
       </c>
       <c r="K11" t="n">
-        <v>75.09731911483969</v>
+        <v>49.27907637371562</v>
       </c>
     </row>
   </sheetData>
